--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, maman accompagne Océane au parc. L'herbe sent la rosée. Une amie arrive. Elle a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Océane regarde. Un autre enfant laisse sortir un petit rire. Maman s'approche tout de suite. Maman dit : on ne va pas rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Océane hoche la tête. Elle va vers l'amie. Océane dit : tu viens au bac à feuilles. Elles ramassent des feuilles. Plus tard, à l'atelier, il y a de la pâte. Océane se souvient. Un enfant regarde encore les lunettes. Océane dit : on ne va pas rire. On joue. Elles roulent la pâte. Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble.</t>
+          <t>Le matin, maman accompagne Océane au parc. L'herbe sent la rosée. Une amie arrive. Elle a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Océane regarde. Un autre enfant laisse sortir un petit rire. Maman s'approche tout de suite. On ne va pas rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Océane hoche la tête. Elle va vers l'amie. Tu viens au bac à feuilles. Elles ramassent des feuilles. Plus tard, à l'atelier, il y a de la pâte. Océane se souvient. Un enfant regarde encore les lunettes. On ne va pas rire. On joue. Elles roulent la pâte. Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, maman accompagne Océane au parc. L'herbe sent la rosée. Une amie arrive. Elle a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Océane regarde. Un autre enfant laisse sortir un petit rire. Maman s'approche tout de suite.
+maman|On ne va pas rire de l'apparence.
+narrateur|Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Océane hoche la tête. Elle va vers l'amie.
+enfant-f|Tu viens au bac à feuilles. Elles ramassent des feuilles. Plus tard, à l'atelier, il y a de la pâte.
+narrateur|Océane se souvient. Un enfant regarde encore les lunettes.
+enfant-f|On ne va pas rire. On joue. Elles roulent la pâte.
+narrateur|Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|L'amie a des lunettes. Que fait-on ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Océane a entendu maman. On ne va pas rire de l'apparence. Océane a invité l'amie. Elles ont joué.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman revient près du portail. Océane et l'amie se disent à demain.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|L'amie a des lunettes. Que fait-on ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Océane a entendu maman. On ne va pas rire de l'apparence. Océane a invité l'amie. Elles ont joué.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1849,7 @@
           <t>narrateur|Maman revient près du portail. Océane et l'amie se disent à demain.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Océane ne rit pas de l'apparence</t>
+          <t>Le rayon sur le bac à feuilles</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah invite Victorina au bac à feuilles, puis elles roulent la pâte. On joue. On ne rit pas de l'apparence.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, maman accompagne Océane au parc. L'herbe sent la rosée. Une amie arrive. Elle a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Océane regarde. Un autre enfant laisse sortir un petit rire. Maman s'approche tout de suite. On ne va pas rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Océane hoche la tête. Elle va vers l'amie. Tu viens au bac à feuilles. Elles ramassent des feuilles. Plus tard, à l'atelier, il y a de la pâte. Océane se souvient. Un enfant regarde encore les lunettes. On ne va pas rire. On joue. Elles roulent la pâte. Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble.</t>
+          <t>Un rayon passe entre les platanes. Il allume le bac à feuilles. Une feuille jaune tremble. Maman boutonne le gilet de Sarah. Tu es bien au chaud, Sarah ? Oui, maman. Le gilet est doux. L'herbe sent la rosée. Le bois du bac est encore humide. En ce moment, Sarah est au parc avec maman. Victorina arrive près du bac. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. On ne va pas rire de l'apparence. On joue. Sarah va vers Victorina. Tu viens au bac à feuilles ? Oui. Elles ramassent des feuilles. Certaines sont sèches. D'autres sont molles et froides. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Celle-ci est grande. Celle-ci est rouge. Elles font un petit tas. Le gilet jaune reste boutonné. Les lunettes restent sur le nez. Les tresses bougent. Bravo, Sarah. Tu as invité Victorina. C'est du bon travail. Plus tard, la petite maison du parc ouvre. Il y a une table. Sur la table, de la pâte douce. Vous voulez rouler la pâte ? Oui. La pâte est froide et lisse. Elle sent un peu la farine. Sarah fait un boudin. Victorina fait une boule. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ma pâte est longue. Ma pâte est ronde. Deux formes. On joue ensemble. Un peu de farine tombe sur la table. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez un emporte-pièce ? L'étoile. La lune. Elles appuient. L'étoile se dessine. La lune se dessine. Bravo. Vous avez travaillé ensemble. Les lunettes brillent au-dessus de la pâte. Le gilet jaune a un peu de farine. On brosse tout doux. Voilà. Elles rangent les formes. La table redevient calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, maman accompagne Océane au parc. L'herbe sent la rosée. Une amie arrive. Elle a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Océane regarde. Un autre enfant laisse sortir un petit rire. Maman s'approche tout de suite.
+          <t>narrateur|Un rayon passe entre les platanes.
+narrateur|Il allume le bac à feuilles.
+narrateur|Une feuille jaune tremble.
+narrateur|Maman boutonne le gilet de Sarah.
+maman|Tu es bien au chaud, Sarah ?
+enfant-f|Oui, maman.
+maman|Le gilet est doux.
+narrateur|L'herbe sent la rosée.
+narrateur|Le bois du bac est encore humide.
+narrateur|En ce moment, Sarah est au parc avec maman.
+narrateur|Victorina arrive près du bac.
+narrateur|Victorina a des lunettes rondes.
+narrateur|Elle a les cheveux tressés.
+narrateur|Elle porte un gilet jaune.
+maman|On joue ensemble.
 maman|On ne va pas rire de l'apparence.
-narrateur|Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Océane hoche la tête. Elle va vers l'amie.
-enfant-f|Tu viens au bac à feuilles. Elles ramassent des feuilles. Plus tard, à l'atelier, il y a de la pâte.
-narrateur|Océane se souvient. Un enfant regarde encore les lunettes.
-enfant-f|On ne va pas rire. On joue. Elles roulent la pâte.
-narrateur|Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble.</t>
+enfant-f|On joue.
+narrateur|Sarah va vers Victorina.
+enfant-f|Tu viens au bac à feuilles ?
+copine|Oui.
+narrateur|Elles ramassent des feuilles.
+narrateur|Certaines sont sèches.
+narrateur|D'autres sont molles et froides.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+maman|L'habit tient chaud.
+maman|On joue.
+enfant-f|Celle-ci est grande.
+copine|Celle-ci est rouge.
+narrateur|Elles font un petit tas.
+narrateur|Le gilet jaune reste boutonné.
+narrateur|Les lunettes restent sur le nez.
+narrateur|Les tresses bougent.
+maman|Bravo, Sarah.
+maman|Tu as invité Victorina.
+maman|C'est du bon travail.
+narrateur|Plus tard, la petite maison du parc ouvre.
+narrateur|Il y a une table.
+narrateur|Sur la table, de la pâte douce.
+maman|Vous voulez rouler la pâte ?
+enfant-f|Oui.
+narrateur|La pâte est froide et lisse.
+narrateur|Elle sent un peu la farine.
+narrateur|Sarah fait un boudin.
+narrateur|Victorina fait une boule.
+maman|On ne rit pas des lunettes, des cheveux ou d'un habit.
+maman|On joue.
+enfant-f|Ma pâte est longue.
+copine|Ma pâte est ronde.
+maman|Deux formes. On joue ensemble.
+narrateur|Un peu de farine tombe sur la table.
+narrateur|Ça fait un nuage tout petit.
+narrateur|Sarah souffle dessus, tout doux.
+maman|Vous voulez un emporte-pièce ?
+enfant-f|L'étoile.
+copine|La lune.
+narrateur|Elles appuient.
+narrateur|L'étoile se dessine.
+narrateur|La lune se dessine.
+maman|Bravo.
+maman|Vous avez travaillé ensemble.
+narrateur|Les lunettes brillent au-dessus de la pâte.
+narrateur|Le gilet jaune a un peu de farine.
+maman|On brosse tout doux. Voilà.
+narrateur|Elles rangent les formes.
+narrateur|La table redevient calme.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,feuilles,pate</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1421,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>L'amie a des lunettes. Que fait-on ?</t>
+          <t>Victorina a des lunettes. Que fait-on ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|L'amie a des lunettes. Que fait-on ?</t>
+          <t>narrateur|Victorina a des lunettes.
+narrateur|Que fait-on ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Océane a entendu maman. On ne va pas rire de l'apparence. Océane a invité l'amie. Elles ont joué.</t>
+          <t>Sarah a entendu maman. On ne va pas rire de l'apparence. Sarah a invité Victorina. Elles ont joué. Bravo, Sarah. Tu as fait du bon travail. On a roulé la pâte. Oui. Ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1750,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Océane a entendu maman. On ne va pas rire de l'apparence. Océane a invité l'amie. Elles ont joué.</t>
+          <t>narrateur|Sarah a entendu maman.
+narrateur|On ne va pas rire de l'apparence.
+narrateur|Sarah a invité Victorina.
+narrateur|Elles ont joué.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+enfant-f|On a roulé la pâte.
+maman|Oui. Ensemble.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman revient près du portail. Océane et l'amie se disent à demain.</t>
+          <t>Maman revient près du portail. Le platane fait de l'ombre. Vous vous dites à demain ? À demain. À demain. Le gilet jaune part sur le chemin. Sarah donne la main à maman. Tu as les doigts un peu farine. C'est bien.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1925,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman revient près du portail. Océane et l'amie se disent à demain.</t>
+          <t>narrateur|Maman revient près du portail.
+narrateur|Le platane fait de l'ombre.
+maman|Vous vous dites à demain ?
+enfant-f|À demain.
+copine|À demain.
+narrateur|Le gilet jaune part sur le chemin.
+narrateur|Sarah donne la main à maman.
+maman|Tu as les doigts un peu farine. C'est bien.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a ramassé des feuilles. On a roulé la pâte. Bravo. Vous avez joué ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2100,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a ramassé des feuilles.
+enfant-f|On a roulé la pâte.
+maman|Bravo.
+maman|Vous avez joué ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon passe entre les platanes. Il allume le bac à feuilles. Une feuille jaune tremble. Maman boutonne le gilet de Sarah. Tu es bien au chaud, Sarah ? Oui, maman. Le gilet est doux. L'herbe sent la rosée. Le bois du bac est encore humide. En ce moment, Sarah est au parc avec maman. Victorina arrive près du bac. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. On ne va pas rire de l'apparence. On joue. Sarah va vers Victorina. Tu viens au bac à feuilles ? Oui. Elles ramassent des feuilles. Certaines sont sèches. D'autres sont molles et froides. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Celle-ci est grande. Celle-ci est rouge. Elles font un petit tas. Le gilet jaune reste boutonné. Les lunettes restent sur le nez. Les tresses bougent. Bravo, Sarah. Tu as invité Victorina. C'est du bon travail. Plus tard, la petite maison du parc ouvre. Il y a une table. Sur la table, de la pâte douce. Vous voulez rouler la pâte ? Oui. La pâte est froide et lisse. Elle sent un peu la farine. Sarah fait un boudin. Victorina fait une boule. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ma pâte est longue. Ma pâte est ronde. Deux formes. On joue ensemble. Un peu de farine tombe sur la table. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez un emporte-pièce ? L'étoile. La lune. Elles appuient. L'étoile se dessine. La lune se dessine. Bravo. Vous avez travaillé ensemble. Les lunettes brillent au-dessus de la pâte. Le gilet jaune a un peu de farine. On brosse tout doux. Voilà. Elles rangent les formes. La table redevient calme.</t>
+          <t>Un rayon passe entre les platanes. Il allume le bac à feuilles. Une feuille jaune tremble. Maman boutonne le gilet de Sarah. Tu es bien au chaud, Sarah ? Oui, maman. Le gilet est doux. L'herbe sent la rosée. Le bois du bac est encore humide. En ce moment, Sarah est au parc avec maman. Victorina arrive près du bac. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. On ne va pas rire de l'apparence. On joue. Sarah va vers Victorina. Tu viens au bac à feuilles ? Oui. Elles ramassent des feuilles. Certaines sont sèches. D'autres sont molles et froides. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Celle-ci est grande. Celle-ci est rouge. Elles font un petit tas. Le gilet jaune reste boutonné. Les lunettes restent sur le nez. Les tresses bougent. Bravo, Sarah. Tu as invité Victorina. C'est du bon travail. Plus tard, la petite maison du parc ouvre. Il y a une table. Sur la table, de la pâte douce. Vous voulez rouler la pâte ? Oui. La pâte est froide et lisse. Elle sent un peu la farine. Sarah fait un boudin. Victorina fait une boule. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ma pâte est longue. Ma pâte est ronde. Deux formes. On joue ensemble. Un peu de farine tombe sur la table. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez un emporte-pièce ? L'étoile. La lune. Elles appuient. L'étoile se dessine. La lune se dessine. Bravo. Vous avez travaillé ensemble. Les lunettes brillent au-dessus de la pâte. Le gilet jaune a un peu de farine. On brosse tout doux. Voilà. Elles rangent les formes. La pâte est froide, hein ? Oui. Froide. Et douce. Vous voulez laver les mains ? Oui. L'eau de la bassine est tiède. Elle fait un petit bruit. Sarah frotte. Victorina frotte. Bravo. Les mains sont propres. Un peu de farine reste sur le gilet jaune. On brosse encore. Voilà. On refait une étoile ? Une dernière. Puis on range. Sarah appuie l'étoile. Victorina appuie la lune. Deux formes. Ensemble. Elles posent les formes sur une assiette. L'assiette est blanche et mate. Vous avez travaillé. C'est du bon travail. On a joué. Oui. On a joué. La table redevient calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1373,7 +1373,8 @@
 maman|On joue.
 enfant-f|Ma pâte est longue.
 copine|Ma pâte est ronde.
-maman|Deux formes. On joue ensemble.
+maman|Deux formes.
+maman|On joue ensemble.
 narrateur|Un peu de farine tombe sur la table.
 narrateur|Ça fait un nuage tout petit.
 narrateur|Sarah souffle dessus, tout doux.
@@ -1387,8 +1388,38 @@
 maman|Vous avez travaillé ensemble.
 narrateur|Les lunettes brillent au-dessus de la pâte.
 narrateur|Le gilet jaune a un peu de farine.
-maman|On brosse tout doux. Voilà.
+maman|On brosse tout doux.
+maman|Voilà.
 narrateur|Elles rangent les formes.
+maman|La pâte est froide, hein ?
+enfant-f|Oui.
+enfant-f|Froide.
+copine|Et douce.
+maman|Vous voulez laver les mains ?
+enfant-f|Oui.
+narrateur|L'eau de la bassine est tiède.
+narrateur|Elle fait un petit bruit.
+narrateur|Sarah frotte.
+narrateur|Victorina frotte.
+maman|Bravo.
+maman|Les mains sont propres.
+narrateur|Un peu de farine reste sur le gilet jaune.
+maman|On brosse encore.
+maman|Voilà.
+enfant-f|On refait une étoile ?
+maman|Une dernière.
+maman|Puis on range.
+narrateur|Sarah appuie l'étoile.
+narrateur|Victorina appuie la lune.
+maman|Deux formes.
+maman|Ensemble.
+narrateur|Elles posent les formes sur une assiette.
+narrateur|L'assiette est blanche et mate.
+maman|Vous avez travaillé.
+maman|C'est du bon travail.
+enfant-f|On a joué.
+maman|Oui.
+maman|On a joué.
 narrateur|La table redevient calme.</t>
         </is>
       </c>
@@ -1606,7 +1637,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a entendu maman. On ne va pas rire de l'apparence. Sarah a invité Victorina. Elles ont joué. Bravo, Sarah. Tu as fait du bon travail. On a roulé la pâte. Oui. Ensemble.</t>
+          <t>Sarah a entendu maman. On ne va pas rire de l'apparence. Sarah a invité Victorina. Elles ont joué. Bravo, Sarah. Tu as fait du bon travail. On a roulé la pâte. Oui. Ensemble. Tu as invité Victorina. Bravo. L'étoile et la lune restent sur l'assiette. Tu as fini de rouler un moment ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1757,7 +1788,13 @@
 maman|Bravo, Sarah.
 maman|Tu as fait du bon travail.
 enfant-f|On a roulé la pâte.
-maman|Oui. Ensemble.</t>
+maman|Oui.
+maman|Ensemble.
+maman|Tu as invité Victorina.
+maman|Bravo.
+narrateur|L'étoile et la lune restent sur l'assiette.
+maman|Tu as fini de rouler un moment ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1932,7 +1969,8 @@
 copine|À demain.
 narrateur|Le gilet jaune part sur le chemin.
 narrateur|Sarah donne la main à maman.
-maman|Tu as les doigts un peu farine. C'est bien.</t>
+maman|Tu as les doigts un peu farine.
+maman|C'est bien.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -2126,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2207,27 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le rayon sur le bac à feuilles</t>
+          <t>L'étoile et la feuille</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah invite Victorina au bac à feuilles, puis elles roulent la pâte. On joue. On ne rit pas de l'apparence.</t>
+          <t>Sarah veut une étoile de pâte avec une vraie feuille dessus. La première feuille s'effrite. Victorina en trouve une souple. L'étoile repose sur l'assiette.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon passe entre les platanes. Il allume le bac à feuilles. Une feuille jaune tremble. Maman boutonne le gilet de Sarah. Tu es bien au chaud, Sarah ? Oui, maman. Le gilet est doux. L'herbe sent la rosée. Le bois du bac est encore humide. En ce moment, Sarah est au parc avec maman. Victorina arrive près du bac. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. On ne va pas rire de l'apparence. On joue. Sarah va vers Victorina. Tu viens au bac à feuilles ? Oui. Elles ramassent des feuilles. Certaines sont sèches. D'autres sont molles et froides. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Celle-ci est grande. Celle-ci est rouge. Elles font un petit tas. Le gilet jaune reste boutonné. Les lunettes restent sur le nez. Les tresses bougent. Bravo, Sarah. Tu as invité Victorina. C'est du bon travail. Plus tard, la petite maison du parc ouvre. Il y a une table. Sur la table, de la pâte douce. Vous voulez rouler la pâte ? Oui. La pâte est froide et lisse. Elle sent un peu la farine. Sarah fait un boudin. Victorina fait une boule. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ma pâte est longue. Ma pâte est ronde. Deux formes. On joue ensemble. Un peu de farine tombe sur la table. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez un emporte-pièce ? L'étoile. La lune. Elles appuient. L'étoile se dessine. La lune se dessine. Bravo. Vous avez travaillé ensemble. Les lunettes brillent au-dessus de la pâte. Le gilet jaune a un peu de farine. On brosse tout doux. Voilà. Elles rangent les formes. La pâte est froide, hein ? Oui. Froide. Et douce. Vous voulez laver les mains ? Oui. L'eau de la bassine est tiède. Elle fait un petit bruit. Sarah frotte. Victorina frotte. Bravo. Les mains sont propres. Un peu de farine reste sur le gilet jaune. On brosse encore. Voilà. On refait une étoile ? Une dernière. Puis on range. Sarah appuie l'étoile. Victorina appuie la lune. Deux formes. Ensemble. Elles posent les formes sur une assiette. L'assiette est blanche et mate. Vous avez travaillé. C'est du bon travail. On a joué. Oui. On a joué. La table redevient calme.</t>
+          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Ses lunettes aident à voir. Celle-ci. Elle est encore molle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le matin, maman accompagne Océane au parc. L'herbe sent la rosée. Une amie arrive. Elle a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Océane regarde. Un autre enfant laisse sortir un petit rire. Maman s'approche tout de suite. Maman dit : on ne va &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Océane hoche la tête. Elle va vers l'amie. Océane dit : tu viens au bac à feuilles. Elles ramassent des feuilles. Plus tard, à l'atelier, il y a de la pâte. Océane se souvient. Un enfant regarde encore les lunettes. Océane dit : on ne va pas rire. On joue. Elles roulent la pâte. Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Ses lunettes aident à voir. Celle-ci. Elle est encore molle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,108 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un rayon passe entre les platanes.
-narrateur|Il allume le bac à feuilles.
-narrateur|Une feuille jaune tremble.
+          <t>narrateur|Le toboggan du parc a un peu de givre.
+narrateur|Il est froid sous le doigt.
+narrateur|Le souffle de Sarah fait un nuage.
+narrateur|La petite maison sent le savon.
 narrateur|Maman boutonne le gilet de Sarah.
+narrateur|Le gilet est doux et épais.
+narrateur|Un oiseau crie tout près.
 maman|Tu es bien au chaud, Sarah ?
 enfant-f|Oui, maman.
-maman|Le gilet est doux.
+maman|Tes mains sont froides.
+enfant-f|Un peu.
+maman|On les frotte.
+narrateur|Sarah frotte ses mains.
+narrateur|Elles redeviennent tièdes.
+narrateur|En ce moment, Sarah cherche une feuille.
 narrateur|L'herbe sent la rosée.
-narrateur|Le bois du bac est encore humide.
-narrateur|En ce moment, Sarah est au parc avec maman.
-narrateur|Victorina arrive près du bac.
+enfant-f|Je veux une étoile.
+enfant-f|Avec une feuille dessus.
+maman|On la presse dans la pâte ?
+enfant-f|Oui.
+maman|Une vraie nervure, alors.
+narrateur|Victorina arrive près du toboggan.
 narrateur|Victorina a des lunettes rondes.
 narrateur|Elle a les cheveux tressés.
 narrateur|Elle porte un gilet jaune.
 maman|On joue ensemble.
-maman|On ne va pas rire de l'apparence.
-enfant-f|On joue.
-narrateur|Sarah va vers Victorina.
-enfant-f|Tu viens au bac à feuilles ?
+enfant-f|Tu m'aides, Victorina ?
 copine|Oui.
-narrateur|Elles ramassent des feuilles.
-narrateur|Certaines sont sèches.
-narrateur|D'autres sont molles et froides.
-maman|Les lunettes aident à voir.
-maman|Les cheveux sont les cheveux.
-maman|L'habit tient chaud.
-maman|On joue.
-enfant-f|Celle-ci est grande.
-copine|Celle-ci est rouge.
-narrateur|Elles font un petit tas.
-narrateur|Le gilet jaune reste boutonné.
-narrateur|Les lunettes restent sur le nez.
-narrateur|Les tresses bougent.
-maman|Bravo, Sarah.
-maman|Tu as invité Victorina.
-maman|C'est du bon travail.
-narrateur|Plus tard, la petite maison du parc ouvre.
-narrateur|Il y a une table.
-narrateur|Sur la table, de la pâte douce.
-maman|Vous voulez rouler la pâte ?
-enfant-f|Oui.
-narrateur|La pâte est froide et lisse.
-narrateur|Elle sent un peu la farine.
-narrateur|Sarah fait un boudin.
-narrateur|Victorina fait une boule.
-maman|On ne rit pas des lunettes, des cheveux ou d'un habit.
-maman|On joue.
-enfant-f|Ma pâte est longue.
-copine|Ma pâte est ronde.
-maman|Deux formes.
-maman|On joue ensemble.
-narrateur|Un peu de farine tombe sur la table.
-narrateur|Ça fait un nuage tout petit.
-narrateur|Sarah souffle dessus, tout doux.
-maman|Vous voulez un emporte-pièce ?
-enfant-f|L'étoile.
-copine|La lune.
-narrateur|Elles appuient.
-narrateur|L'étoile se dessine.
-narrateur|La lune se dessine.
-maman|Bravo.
-maman|Vous avez travaillé ensemble.
-narrateur|Les lunettes brillent au-dessus de la pâte.
-narrateur|Le gilet jaune a un peu de farine.
-maman|On brosse tout doux.
-maman|Voilà.
-narrateur|Elles rangent les formes.
-maman|La pâte est froide, hein ?
-enfant-f|Oui.
-enfant-f|Froide.
-copine|Et douce.
-maman|Vous voulez laver les mains ?
-enfant-f|Oui.
-narrateur|L'eau de la bassine est tiède.
-narrateur|Elle fait un petit bruit.
-narrateur|Sarah frotte.
-narrateur|Victorina frotte.
-maman|Bravo.
-maman|Les mains sont propres.
-narrateur|Un peu de farine reste sur le gilet jaune.
-maman|On brosse encore.
-maman|Voilà.
-enfant-f|On refait une étoile ?
-maman|Une dernière.
-maman|Puis on range.
-narrateur|Sarah appuie l'étoile.
-narrateur|Victorina appuie la lune.
-maman|Deux formes.
-maman|Ensemble.
-narrateur|Elles posent les formes sur une assiette.
-narrateur|L'assiette est blanche et mate.
-maman|Vous avez travaillé.
-maman|C'est du bon travail.
-enfant-f|On a joué.
-maman|Oui.
-maman|On a joué.
-narrateur|La table redevient calme.</t>
+narrateur|Sarah ramasse une feuille jaune.
+narrateur|Elle est sèche et fragile.
+narrateur|Elle s'effrite entre les doigts.
+narrateur|Un peu de jaune reste sur la main.
+enfant-f|Elle casse.
+maman|On en cherche une souple.
+narrateur|Victorina se penche.
+narrateur|Ses lunettes aident à voir.
+copine|Celle-ci.
+copine|Elle est encore molle.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc,feuilles,pate</t>
+          <t>enfants_parc,pate</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1398,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'amie a des lunettes. Que fait-on ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a des lunettes. Que fait-on ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1467,12 +1408,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>pas rire</t>
+          <t>jouer</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>pas rire | on joue | jouer | pas rire apparence</t>
+          <t>jouer | ensemble | feuille | on joue | presser | pas rire</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1487,7 +1428,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On joue. On ne va pas rire. Que fait-on ?</t>
+          <t>On cherche une feuille souple. Que fait-on ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1529,14 +1470,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1553,6 @@
 narrateur|Que fait-on ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1637,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a entendu maman. On ne va pas rire de l'apparence. Sarah a invité Victorina. Elles ont joué. Bravo, Sarah. Tu as fait du bon travail. On a roulé la pâte. Oui. Ensemble. Tu as invité Victorina. Bravo. L'étoile et la lune restent sur l'assiette. Tu as fini de rouler un moment ? Oui.</t>
+          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Les lunettes aident à voir. On joue. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Océane a entendu maman. On ne va &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; rire de l'apparence. Océane a invité l'amie. Elles ont joué.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Les lunettes aident à voir. On joue. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1705,7 +1645,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1781,23 +1721,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a entendu maman.
-narrateur|On ne va pas rire de l'apparence.
-narrateur|Sarah a invité Victorina.
-narrateur|Elles ont joué.
-maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
-enfant-f|On a roulé la pâte.
+          <t>narrateur|Sarah prend la feuille souple.
+narrateur|Elle la pose dans sa main.
+maman|Merci, Sarah.
+maman|Merci, Victorina.
+enfant-f|On va à la petite maison ?
 maman|Oui.
-maman|Ensemble.
-maman|Tu as invité Victorina.
-maman|Bravo.
-narrateur|L'étoile et la lune restent sur l'assiette.
-maman|Tu as fini de rouler un moment ?
-enfant-f|Oui.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|La pâte nous attend.
+narrateur|La table est froide et lisse.
+narrateur|La pâte sent la farine.
+narrateur|Elle colle un peu aux doigts.
+maman|Les lunettes aident à voir.
+maman|On joue.
+narrateur|Sarah fait un boudin.
+narrateur|Victorina fait une boule.
+enfant-f|L'étoile.
+copine|La feuille.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1822,12 +1763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman revient près du portail. Le platane fait de l'ombre. Vous vous dites à demain ? À demain. À demain. Le gilet jaune part sur le chemin. Sarah donne la main à maman. Tu as les doigts un peu farine. C'est bien.</t>
+          <t>Sarah appuie l'emporte-pièce. L'étoile se dessine. Victorina pose la feuille. Sarah presse tout doux. La nervure s'imprime dans la pâte. Elle est restée ! On voit les traits. Bravo. Vous avez pressé ensemble. Un peu de farine tombe. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez laver les mains ? Oui. L'eau de la bassine est tiède. Sarah frotte. Victorina frotte. Elles posent l'étoile sur l'assiette. L'assiette est blanche et mate. Ma feuille est dessus. Oui. Elle est souple. On voit même les bords. Un peu de givre fond dehors.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman revient près du portail. Océane et l'amie se disent à de&lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah appuie l'emporte-pièce. L'étoile se dessine. Victorina pose la feuille. Sarah presse tout doux. La nervure s'imprime dans la pâte. Elle est restée ! On voit les traits. Bravo. Vous avez pressé ensemble. Un peu de farine tombe. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez laver les mains ? Oui. L'eau de la bassine est tiède. Sarah frotte. Victorina frotte. Elles posent l'étoile sur l'assiette. L'assiette est blanche et mate. Ma feuille est dessus. Oui. Elle est souple. On voit même les bords. Un peu de givre fond dehors.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1890,7 +1831,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1962,18 +1903,32 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman revient près du portail.
-narrateur|Le platane fait de l'ombre.
-maman|Vous vous dites à demain ?
-enfant-f|À demain.
-copine|À demain.
-narrateur|Le gilet jaune part sur le chemin.
-narrateur|Sarah donne la main à maman.
-maman|Tu as les doigts un peu farine.
-maman|C'est bien.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah appuie l'emporte-pièce.
+narrateur|L'étoile se dessine.
+narrateur|Victorina pose la feuille.
+narrateur|Sarah presse tout doux.
+narrateur|La nervure s'imprime dans la pâte.
+enfant-f|Elle est restée !
+copine|On voit les traits.
+maman|Bravo.
+maman|Vous avez pressé ensemble.
+narrateur|Un peu de farine tombe.
+narrateur|Ça fait un nuage tout petit.
+narrateur|Sarah souffle dessus, tout doux.
+maman|Vous voulez laver les mains ?
+enfant-f|Oui.
+narrateur|L'eau de la bassine est tiède.
+narrateur|Sarah frotte.
+narrateur|Victorina frotte.
+narrateur|Elles posent l'étoile sur l'assiette.
+narrateur|L'assiette est blanche et mate.
+enfant-f|Ma feuille est dessus.
+maman|Oui.
+maman|Elle est souple.
+copine|On voit même les bords.
+narrateur|Un peu de givre fond dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a ramassé des feuilles. On a roulé la pâte. Bravo. Vous avez joué ensemble. L'histoire est finie.</t>
+          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez joué ensemble. Le givre fond sur le toboggan. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez joué ensemble. Le givre fond sur le toboggan. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2066,7 +2021,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2138,14 +2093,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|On a ramassé des feuilles.
-enfant-f|On a roulé la pâte.
-maman|Bravo.
+          <t>narrateur|L'étoile repose sur l'assiette.
+narrateur|La feuille jaune est bien pressée.
+enfant-f|On l'a faite.
+maman|Oui.
 maman|Vous avez joué ensemble.
+narrateur|Le givre fond sur le toboggan.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2164,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2230,6 +2186,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Ses lunettes aident à voir. Celle-ci. Elle est encore molle.</t>
+          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Victorina, tu cherches aussi. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Elle choisit une feuille molle. Celle-ci. Elle est encore molle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. On joue ensemble. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Ses lunettes aident à voir. Celle-ci. Elle est encore molle.</t>
+          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Victorina, tu cherches aussi. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Elle choisit une feuille molle. Celle-ci. Elle est encore molle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
 narrateur|Victorina a des lunettes rondes.
 narrateur|Elle a les cheveux tressés.
 narrateur|Elle porte un gilet jaune.
-maman|On joue ensemble.
+maman|Victorina, tu cherches aussi.
 enfant-f|Tu m'aides, Victorina ?
 copine|Oui.
 narrateur|Sarah ramasse une feuille jaune.
@@ -1359,7 +1359,7 @@
 enfant-f|Elle casse.
 maman|On en cherche une souple.
 narrateur|Victorina se penche.
-narrateur|Ses lunettes aident à voir.
+narrateur|Elle choisit une feuille molle.
 copine|Celle-ci.
 copine|Elle est encore molle.</t>
         </is>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Les lunettes aident à voir. On joue. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
+          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Victorina a trouvé la souple. On presse. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Les lunettes aident à voir. On joue. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
+          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Victorina a trouvé la souple. On presse. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1731,8 +1731,8 @@
 narrateur|La table est froide et lisse.
 narrateur|La pâte sent la farine.
 narrateur|Elle colle un peu aux doigts.
-maman|Les lunettes aident à voir.
-maman|On joue.
+maman|Victorina a trouvé la souple.
+maman|On presse.
 narrateur|Sarah fait un boudin.
 narrateur|Victorina fait une boule.
 enfant-f|L'étoile.
@@ -1953,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez joué ensemble. Le givre fond sur le toboggan. L'histoire est finie.</t>
+          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez joué ensemble. Le givre fond sur le toboggan. L'histoire est finie.</t>
+          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
 narrateur|La feuille jaune est bien pressée.
 enfant-f|On l'a faite.
 maman|Oui.
-maman|Vous avez joué ensemble.
+maman|Vous avez pressé l'étoile.
 narrateur|Le givre fond sur le toboggan.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -2120,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2191,6 +2191,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -1953,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan. L'histoire est finie.</t>
+          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan. L'histoire est finie.</t>
+          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,8 +2098,7 @@
 enfant-f|On l'a faite.
 maman|Oui.
 maman|Vous avez pressé l'étoile.
-narrateur|Le givre fond sur le toboggan.
-narrateur|L'histoire est finie.</t>
+narrateur|Le givre fond sur le toboggan.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2198,6 +2197,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc puis atelier</t>
+          <t>parc le matin, puis petite maison</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Océane, maman</t>
+          <t>Sarah, Victorina, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-04.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc le matin, puis petite maison</t>
+          <t>parc sous les platanes, bac à feuilles, puis atelier (pâte, emporte-pièce)</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sarah, Victorina, maman</t>
+          <t>Sarah, Victorina, papa, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah veut une étoile de pâte avec une vraie feuille dessus. La première feuille s'effrite. Victorina en trouve une souple. L'étoile repose sur l'assiette.</t>
+          <t>Un platane lâche un petit bruit, sec. Sur le bord du bac, un éclat de platane brille. Sarah veut une étoile avec une feuille, maintenant. Victorina arrive. Un rire commence. Victorina se tait. La feuille sèche casse. Sarah refuse de foncer. Elles portent la souple. Merci vécu. L'emporte-pièce trop vite. L'éclat de platane tient sur la manche.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Victorina, tu cherches aussi. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Elle choisit une feuille molle. Celle-ci. Elle est encore molle.</t>
+          <t>Un platane lâche un petit bruit, sec. J'ai entendu, papa ! Tu as entendu le platane ? Oui, un petit bruit. Un éclat pâle glisse le long du tronc. Il brille, maman. Tu le vois, le petit point ? Oui, pâle. Il s'arrête sur le bord du bac. Sur le bord du bac, un éclat de platane brille. Le bac est froid, Sarah ? Un peu, papa. Le bac sent le platane, un peu humide. Tes mains sont froides, Sarah ? Un peu. On les frotte ? Oui. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. Je veux une étoile, maintenant ! Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors ? Oui, papa. Victorina arrive près du bac. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Victorina, tu cherches aussi ? Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille trop vite. La feuille est sèche et fragile. Elle s'effrite entre les doigts. Elle casse ! Sarah regarde les lunettes, trop longtemps. Un rire commence dans sa bouche. Victorina ne dit rien. Le sourire de Victorina disparaît. Tu la trouves, maintenant ! Non. Victorina recule d'un pas. Oh. Sarah veut presser toute seule. La feuille sèche tombe dans le bac. Ça fait un bruit mou. L'éclat de platane tremble, puis tient. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Victorina, Sarah ? Oui, papa. Tes mains sont collantes, Sarah ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le toboggan du parc a un peu de givre. Il est froid sous le doigt. Le souffle de Sarah fait un nuage. La petite maison sent le savon. Maman boutonne le gilet de Sarah. Le gilet est doux et épais. Un oiseau crie tout près. Tu es bien au chaud, Sarah ? Oui, maman. Tes mains sont froides. Un peu. On les frotte. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. L'herbe sent la rosée. Je veux une étoile. Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors. Victorina arrive près du toboggan. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Victorina, tu cherches aussi. Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille jaune. Elle est sèche et fragile. Elle s'effrite entre les doigts. Un peu de jaune reste sur la main. Elle casse. On en cherche une souple. Victorina se penche. Elle choisit une feuille molle. Celle-ci. Elle est encore molle.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un platane lâche un petit bruit, sec. J'ai entendu, papa ! Tu as entendu le platane ? Oui, un petit bruit. Un éclat pâle glisse le long du tronc. Il brille, maman. Tu le vois, le petit point ? Oui, pâle. Il s'arrête sur le bord du bac. Sur le bord du bac, un &lt;emphasis level="moderate"&gt;éclat de platane&lt;/emphasis&gt; brille. Le bac est froid, Sarah ? Un peu, papa. Le bac sent le platane, un peu humide. Tes mains sont froides, Sarah ? Un peu. On les frotte ? Oui. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. Je veux une étoile, maintenant ! Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors ? Oui, papa. Victorina arrive près du bac. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Victorina, tu cherches aussi ? Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille trop vite. La feuille est sèche et fragile. Elle s'effrite entre les doigts. Elle casse ! Sarah regarde les lunettes, trop longtemps. Un rire commence dans sa bouche. Victorina ne dit rien. Le sourire de Victorina disparaît. Tu la trouves, maintenant ! Non. Victorina recule d'un pas. Oh. Sarah veut presser toute seule. La feuille sèche tombe dans le bac. Ça fait un bruit mou. L'éclat de platane tremble, puis tient. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Victorina, Sarah ? Oui, papa. Tes mains sont collantes, Sarah ? Un peu, maman.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, maman accompagne Océane au parc. L'herbe sent la rosée. Une amie arrive. Elle a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Océane regarde. Un autre enfant laisse sortir un petit rire. Maman s'approche tout de suite. Maman dit : on ne va &lt;emphasis&gt;pas&lt;/emphasis&gt; rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Océane hoche la tête. Elle va vers l'amie. Océane dit : tu viens au bac à feuilles. Elles ramassent des feuilles. Plus tard, à l'atelier, il y a de la pâte. Océane se souvient. Un enfant regarde encore les lunettes. Océane dit : on ne va pas rire. On joue. Elles roulent la pâte. Les lunettes restent sur le nez. Les tresses bougent. Le gilet jaune reste boutonné. On ne rit pas des lunettes, des cheveux ou d'un habit. On ne va pas rire de l'apparence. On joue ensemble. [pause]</t>
+          <t>Un platane lâche un petit bruit, sec. J'ai entendu, papa ! Tu as entendu le platane ? Oui, un petit bruit. Un éclat pâle glisse le long du tronc. Il brille, maman. Tu le vois, le petit point ? Oui, pâle. Il s'arrête sur le bord du bac. Sur le bord du bac, un &lt;emphasis&gt;éclat de platane&lt;/emphasis&gt; brille. Le bac est froid, Sarah ? Un peu, papa. Le bac sent le platane, un peu humide. Tes mains sont froides, Sarah ? Un peu. On les frotte ? Oui. Sarah frotte ses mains. Elles redeviennent tièdes. En ce moment, Sarah cherche une feuille. Je veux une étoile, maintenant ! Avec une feuille dessus. On la presse dans la pâte ? Oui. Une vraie nervure, alors ? Oui, papa. Victorina arrive près du bac. Victorina a des lunettes rondes. Elle a les cheveux tressés. Elle porte un gilet jaune. Victorina, tu cherches aussi ? Tu m'aides, Victorina ? Oui. Sarah ramasse une feuille trop vite. La feuille est sèche et fragile. Elle s'effrite entre les doigts. Elle casse ! Sarah regarde les lunettes, trop longtemps. Un rire commence dans sa bouche. Victorina ne dit rien. Le sourire de Victorina disparaît. Tu la trouves, maintenant ! Non. Victorina recule d'un pas. Oh. Sarah veut presser toute seule. La feuille sèche tombe dans le bac. Ça fait un bruit mou. L'éclat de platane tremble, puis tient. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Victorina, Sarah ? Oui, papa. Tes mains sont collantes, Sarah ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>éclat de platane</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,47 +1321,70 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_l_etoile_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le toboggan du parc a un peu de givre.
-narrateur|Il est froid sous le doigt.
-narrateur|Le souffle de Sarah fait un nuage.
-narrateur|La petite maison sent le savon.
-narrateur|Maman boutonne le gilet de Sarah.
-narrateur|Le gilet est doux et épais.
-narrateur|Un oiseau crie tout près.
-maman|Tu es bien au chaud, Sarah ?
-enfant-f|Oui, maman.
-maman|Tes mains sont froides.
+          <t>narrateur|Un platane lâche un petit bruit, sec.
+enfant-f|J'ai entendu, papa !
+papa|Tu as entendu le platane ?
+enfant-f|Oui, un petit bruit.
+narrateur|Un éclat pâle glisse le long du tronc.
+enfant-f|Il brille, maman.
+maman|Tu le vois, le petit point ?
+enfant-f|Oui, pâle.
+narrateur|Il s'arrête sur le bord du bac.
+narrateur|Sur le bord du bac, un éclat de platane brille.
+papa|Le bac est froid, Sarah ?
+enfant-f|Un peu, papa.
+narrateur|Le bac sent le platane, un peu humide.
+maman|Tes mains sont froides, Sarah ?
 enfant-f|Un peu.
-maman|On les frotte.
+papa|On les frotte ?
+enfant-f|Oui.
 narrateur|Sarah frotte ses mains.
 narrateur|Elles redeviennent tièdes.
 narrateur|En ce moment, Sarah cherche une feuille.
-narrateur|L'herbe sent la rosée.
-enfant-f|Je veux une étoile.
+enfant-f|Je veux une étoile, maintenant !
 enfant-f|Avec une feuille dessus.
 maman|On la presse dans la pâte ?
 enfant-f|Oui.
-maman|Une vraie nervure, alors.
-narrateur|Victorina arrive près du toboggan.
+papa|Une vraie nervure, alors ?
+enfant-f|Oui, papa.
+narrateur|Victorina arrive près du bac.
 narrateur|Victorina a des lunettes rondes.
 narrateur|Elle a les cheveux tressés.
 narrateur|Elle porte un gilet jaune.
-maman|Victorina, tu cherches aussi.
+papa|Victorina, tu cherches aussi ?
 enfant-f|Tu m'aides, Victorina ?
 copine|Oui.
-narrateur|Sarah ramasse une feuille jaune.
-narrateur|Elle est sèche et fragile.
+narrateur|Sarah ramasse une feuille trop vite.
+narrateur|La feuille est sèche et fragile.
 narrateur|Elle s'effrite entre les doigts.
-narrateur|Un peu de jaune reste sur la main.
-enfant-f|Elle casse.
-maman|On en cherche une souple.
-narrateur|Victorina se penche.
-narrateur|Elle choisit une feuille molle.
-copine|Celle-ci.
-copine|Elle est encore molle.</t>
+enfant-f|Elle casse !
+narrateur|Sarah regarde les lunettes, trop longtemps.
+narrateur|Un rire commence dans sa bouche.
+narrateur|Victorina ne dit rien.
+narrateur|Le sourire de Victorina disparaît.
+enfant-f|Tu la trouves, maintenant !
+copine|Non.
+narrateur|Victorina recule d'un pas.
+enfant-f|Oh.
+narrateur|Sarah veut presser toute seule.
+narrateur|La feuille sèche tombe dans le bac.
+narrateur|Ça fait un bruit mou.
+narrateur|L'éclat de platane tremble, puis tient.
+narrateur|Le sourire de Sarah disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu vois Victorina, Sarah ?
+enfant-f|Oui, papa.
+maman|Tes mains sont collantes, Sarah ?
+enfant-f|Un peu, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1398,22 +1421,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Victorina a des lunettes. Que fait-on ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Victorina a des &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;. Que fait-on ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>L'amie a des lunettes. Que fait-on ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Victorina a des &lt;emphasis&gt;lunettes&lt;/emphasis&gt;. Que fait-on ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>jouer</t>
+          <t>pas rire</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>jouer | ensemble | feuille | on joue | presser | pas rire</t>
+          <t>pas rire | on joue | jouer | pas rire apparence</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1466,7 +1489,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1474,10 +1497,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1492,34 +1515,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>lunettes</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1528,23 +1555,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=on_ne_rit_pas_victorina_a_des_lunettes; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1577,17 +1604,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Victorina a trouvé la souple. On presse. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
+          <t>Sarah veut l'étoile, tout de suite. Je presse, maintenant ! Elle avance trop vite vers Victorina. Les mots se bousculent dans sa bouche. Non. Victorina reste un peu plus loin. Oh. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe le bac, un instant. Elle écoute le petit bruit du platane. Tu veux l'étoile avec Victorina ? Papa reste à la même hauteur. Tu cherches avec moi ? Victorina ne dit rien, d'abord. Elle se penche sur le bac. Celle-ci. Elle est molle. D'accord. Merci, Sarah. Papa a vu les deux, près du bac. La feuille est souple, sous les doigts. Elle ne casse pas. Sarah pose la feuille dans sa main. Victorina reste plus près. On va à l'atelier ? Oui. La pâte nous attend. Tu portes la feuille, Sarah ? Oui, papa. Ils passent sous les platanes. Le gilet jaune bouge. Les tresses tapent le dos. Les lunettes restent sur le nez. La table, maman. Elle est froide et lisse. La pâte colle un peu aux doigts. On étale, sans se presser ? Oui. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille. Tes mains sont au chaud ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend la feuille souple. Elle la pose dans sa main. Merci, Sarah. Merci, Victorina. On va à la petite maison ? Oui. La pâte nous attend. La table est froide et lisse. La pâte sent la farine. Elle colle un peu aux doigts. Victorina a trouvé la souple. On presse. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah veut l'étoile, tout de suite. Je presse, maintenant ! Elle avance trop vite vers Victorina. Les mots se bousculent dans sa bouche. Non. Victorina reste un peu plus loin. Oh. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe le bac, un instant. Elle écoute le petit bruit du platane. Tu veux l'étoile avec Victorina ? Papa reste à la même hauteur. Tu cherches avec moi ? Victorina ne dit rien, d'abord. Elle se penche sur le bac. Celle-ci. Elle est molle. D'accord. Merci, Sarah. Papa a vu les deux, près du bac. La &lt;emphasis level="moderate"&gt;feuille&lt;/emphasis&gt; est souple, sous les doigts. Elle ne casse pas. Sarah pose la feuille dans sa main. Victorina reste plus près. On va à l'atelier ? Oui. La pâte nous attend. Tu portes la feuille, Sarah ? Oui, papa. Ils passent sous les platanes. Le gilet jaune bouge. Les tresses tapent le dos. Les lunettes restent sur le nez. La table, maman. Elle est froide et lisse. La pâte colle un peu aux doigts. On étale, sans se presser ? Oui. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille. Tes mains sont au chaud ? Un peu, maman.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Océane a entendu maman. On ne va &lt;emphasis&gt;pas&lt;/emphasis&gt; rire de l'apparence. Océane a invité l'amie. Elles ont joué. [pause]</t>
+          <t>Sarah veut l'étoile, tout de suite. Je presse, maintenant ! Elle avance trop vite vers Victorina. Les mots se bousculent dans sa bouche. Non. Victorina reste un peu plus loin. Oh. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe le bac, un instant. Elle écoute le petit bruit du platane. Tu veux l'étoile avec Victorina ? Papa reste à la même hauteur. Tu cherches avec moi ? Victorina ne dit rien, d'abord. Elle se penche sur le bac. Celle-ci. Elle est molle. D'accord. Merci, Sarah. Papa a vu les deux, près du bac. La &lt;emphasis&gt;feuille&lt;/emphasis&gt; est souple, sous les doigts. Elle ne casse pas. Sarah pose la feuille dans sa main. Victorina reste plus près. On va à l'atelier ? Oui. La pâte nous attend. Tu portes la feuille, Sarah ? Oui, papa. Ils passent sous les platanes. Le gilet jaune bouge. Les tresses tapent le dos. Les lunettes restent sur le nez. La table, maman. Elle est froide et lisse. La pâte colle un peu aux doigts. On étale, sans se presser ? Oui. Sarah fait un boudin. Victorina fait une boule. L'étoile. La feuille. Tes mains sont au chaud ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1634,7 +1661,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1642,10 +1669,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1668,30 +1695,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>feuille</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1700,10 +1727,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1716,27 +1743,63 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elles_portent_la_feuille_a_deux; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah prend la feuille souple.
-narrateur|Elle la pose dans sa main.
-maman|Merci, Sarah.
-maman|Merci, Victorina.
-enfant-f|On va à la petite maison ?
+          <t>narrateur|Sarah veut l'étoile, tout de suite.
+enfant-f|Je presse, maintenant !
+narrateur|Elle avance trop vite vers Victorina.
+narrateur|Les mots se bousculent dans sa bouche.
+copine|Non.
+narrateur|Victorina reste un peu plus loin.
+enfant-f|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Sarah refuse de foncer.
+narrateur|Elle referme la bouche.
+narrateur|Personne ne parle.
+narrateur|Elle observe le bac, un instant.
+narrateur|Elle écoute le petit bruit du platane.
+papa|Tu veux l'étoile avec Victorina ?
+narrateur|Papa reste à la même hauteur.
+enfant-f|Tu cherches avec moi ?
+narrateur|Victorina ne dit rien, d'abord.
+narrateur|Elle se penche sur le bac.
+copine|Celle-ci.
+copine|Elle est molle.
+enfant-f|D'accord.
+papa|Merci, Sarah.
+narrateur|Papa a vu les deux, près du bac.
+maman|La feuille est souple, sous les doigts.
+enfant-f|Elle ne casse pas.
+narrateur|Sarah pose la feuille dans sa main.
+narrateur|Victorina reste plus près.
+enfant-f|On va à l'atelier ?
 maman|Oui.
 maman|La pâte nous attend.
-narrateur|La table est froide et lisse.
-narrateur|La pâte sent la farine.
-narrateur|Elle colle un peu aux doigts.
-maman|Victorina a trouvé la souple.
-maman|On presse.
+papa|Tu portes la feuille, Sarah ?
+enfant-f|Oui, papa.
+narrateur|Ils passent sous les platanes.
+narrateur|Le gilet jaune bouge.
+narrateur|Les tresses tapent le dos.
+narrateur|Les lunettes restent sur le nez.
+enfant-f|La table, maman.
+maman|Elle est froide et lisse.
+narrateur|La pâte colle un peu aux doigts.
+papa|On étale, sans se presser ?
+enfant-f|Oui.
 narrateur|Sarah fait un boudin.
 narrateur|Victorina fait une boule.
 enfant-f|L'étoile.
-copine|La feuille.</t>
+copine|La feuille.
+maman|Tes mains sont au chaud ?
+enfant-f|Un peu, maman.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>pate</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1826,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah appuie l'emporte-pièce. L'étoile se dessine. Victorina pose la feuille. Sarah presse tout doux. La nervure s'imprime dans la pâte. Elle est restée ! On voit les traits. Bravo. Vous avez pressé ensemble. Un peu de farine tombe. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez laver les mains ? Oui. L'eau de la bassine est tiède. Sarah frotte. Victorina frotte. Elles posent l'étoile sur l'assiette. L'assiette est blanche et mate. Ma feuille est dessus. Oui. Elle est souple. On voit même les bords. Un peu de givre fond dehors.</t>
+          <t>Sarah prend l'emporte-pièce. Le métal est froid, un peu lourd. L'étoile, maintenant ! Elle appuie trop vite, tout de suite. Elle regarde les lunettes, trop longtemps. Un rire revient dans sa bouche. Attends. Victorina lâche le bord de la pâte. La feuille glisse sur le côté. Ça part ! Sarah avance les mains, trop vite. Puis elle s'arrête net. Sarah refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe la pâte, un instant. Elle écoute le petit bruit du platane. Sur la manche, un éclat de platane luit. Là, sur la manche. Tu poses la feuille, Victorina ? Victorina ne dit rien. Elle reprend le bord, sans parler. Oui. Sarah appuie, sans se presser. Victorina pose la feuille. La nervure s'imprime dans la pâte. Elle est restée ! On voit les traits. Tu as pressé sans t'arrêter ? Oui, papa. Le gilet est chaud, Victorina ? Un peu. Un peu de pâte tombe. Ça fait un nuage tout petit. On pose l'étoile ? Sur l'assiette. L'assiette est blanche et mate. Ma feuille est dessus. Oui. Elle est souple. On voit même les bords. La pâte a tenu, Sarah ? Oui, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sarah appuie l'emporte-pièce. L'étoile se dessine. Victorina pose la feuille. Sarah presse tout doux. La nervure s'imprime dans la pâte. Elle est restée ! On voit les traits. Bravo. Vous avez pressé ensemble. Un peu de farine tombe. Ça fait un nuage tout petit. Sarah souffle dessus, tout doux. Vous voulez laver les mains ? Oui. L'eau de la bassine est tiède. Sarah frotte. Victorina frotte. Elles posent l'étoile sur l'assiette. L'assiette est blanche et mate. Ma feuille est dessus. Oui. Elle est souple. On voit même les bords. Un peu de givre fond dehors.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah prend l'emporte-pièce. Le métal est froid, un peu lourd. L'étoile, maintenant ! Elle appuie trop vite, tout de suite. Elle regarde les lunettes, trop longtemps. Un rire revient dans sa bouche. Attends. Victorina lâche le bord de la pâte. La feuille glisse sur le côté. Ça part ! Sarah avance les mains, trop vite. Puis elle s'arrête net. Sarah refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe la pâte, un instant. Elle écoute le petit bruit du platane. Sur la manche, un &lt;emphasis level="moderate"&gt;éclat de platane&lt;/emphasis&gt; luit. Là, sur la manche. Tu poses la feuille, Victorina ? Victorina ne dit rien. Elle reprend le bord, sans parler. Oui. Sarah appuie, sans se presser. Victorina pose la feuille. La nervure s'imprime dans la pâte. Elle est restée ! On voit les traits. Tu as pressé sans t'arrêter ? Oui, papa. Le gilet est chaud, Victorina ? Un peu. Un peu de pâte tombe. Ça fait un nuage tout petit. On pose l'étoile ? Sur l'assiette. L'assiette est blanche et mate. Ma feuille est dessus. Oui. Elle est souple. On voit même les bords. La pâte a tenu, Sarah ? Oui, papa.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman revient près du portail. Océane et l'amie se disent à de&lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>Sarah prend l'emporte-pièce. Le métal est froid, un peu lourd. L'étoile, maintenant ! Elle appuie trop vite, tout de suite. Elle regarde les lunettes, trop longtemps. Un rire revient dans sa bouche. Attends. Victorina lâche le bord de la pâte. La feuille glisse sur le côté. Ça part ! Sarah avance les mains, trop vite. Puis elle s'arrête net. Sarah refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe la pâte, un instant. Elle écoute le petit bruit du platane. Sur la manche, un &lt;emphasis&gt;éclat de platane&lt;/emphasis&gt; luit. Là, sur la manche. Tu poses la feuille, Victorina ? Victorina ne dit rien. Elle reprend le bord, sans parler. Oui. Sarah appuie, sans se presser. Victorina pose la feuille. La nervure s'imprime dans la pâte. Elle est restée ! On voit les traits. Tu as pressé sans t'arrêter ? Oui, papa. Le gilet est chaud, Victorina ? Un peu. Un peu de pâte tombe. Ça fait un nuage tout petit. On pose l'étoile ? Sur l'assiette. L'assiette est blanche et mate. Ma feuille est dessus. Oui. Elle est souple. On voit même les bords. La pâte a tenu, Sarah ? Oui, papa. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1820,7 +1883,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1828,10 +1891,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1854,30 +1917,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de platane</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1886,10 +1949,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1900,33 +1963,61 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_l_eclat; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sarah appuie l'emporte-pièce.
-narrateur|L'étoile se dessine.
+          <t>narrateur|Sarah prend l'emporte-pièce.
+narrateur|Le métal est froid, un peu lourd.
+enfant-f|L'étoile, maintenant !
+narrateur|Elle appuie trop vite, tout de suite.
+narrateur|Elle regarde les lunettes, trop longtemps.
+narrateur|Un rire revient dans sa bouche.
+copine|Attends.
+narrateur|Victorina lâche le bord de la pâte.
+narrateur|La feuille glisse sur le côté.
+enfant-f|Ça part !
+narrateur|Sarah avance les mains, trop vite.
+narrateur|Puis elle s'arrête net.
+narrateur|Sarah refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Personne ne dit la suite.
+narrateur|Elle observe la pâte, un instant.
+narrateur|Elle écoute le petit bruit du platane.
+narrateur|Sur la manche, un éclat de platane luit.
+enfant-f|Là, sur la manche.
+enfant-f|Tu poses la feuille, Victorina ?
+narrateur|Victorina ne dit rien.
+narrateur|Elle reprend le bord, sans parler.
+copine|Oui.
+narrateur|Sarah appuie, sans se presser.
 narrateur|Victorina pose la feuille.
-narrateur|Sarah presse tout doux.
 narrateur|La nervure s'imprime dans la pâte.
 enfant-f|Elle est restée !
 copine|On voit les traits.
-maman|Bravo.
-maman|Vous avez pressé ensemble.
-narrateur|Un peu de farine tombe.
+papa|Tu as pressé sans t'arrêter ?
+enfant-f|Oui, papa.
+maman|Le gilet est chaud, Victorina ?
+copine|Un peu.
+narrateur|Un peu de pâte tombe.
 narrateur|Ça fait un nuage tout petit.
-narrateur|Sarah souffle dessus, tout doux.
-maman|Vous voulez laver les mains ?
-enfant-f|Oui.
-narrateur|L'eau de la bassine est tiède.
-narrateur|Sarah frotte.
-narrateur|Victorina frotte.
-narrateur|Elles posent l'étoile sur l'assiette.
+papa|On pose l'étoile ?
+copine|Sur l'assiette.
 narrateur|L'assiette est blanche et mate.
 enfant-f|Ma feuille est dessus.
 maman|Oui.
 maman|Elle est souple.
 copine|On voit même les bords.
-narrateur|Un peu de givre fond dehors.</t>
+papa|La pâte a tenu, Sarah ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>pate</t>
         </is>
       </c>
     </row>
@@ -1953,17 +2044,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan.</t>
+          <t>Ils restent près de la table. Maman essuie un peu de pâte. On a eu l'étoile, papa. Tu l'as vue, toi ? Oui, avec la feuille. On est bien, ici. Sarah tapote l'étoile du doigt. Elle a une trace de nervure. Tu la vois, la trace ? Oui, maman. L'étoile est restée, Sarah. Oui, avec Victorina. L'étoile est restée. Ça sent le platane, un peu tiède. Et la pâte, maman. Oui, dans l'air. La feuille reste sur l'étoile. Un éclat de platane tient sur la manche.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>L'étoile repose sur l'assiette. La feuille jaune est bien pressée. On l'a faite. Oui. Vous avez pressé l'étoile. Le givre fond sur le toboggan.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent près de la table. Maman essuie un peu de pâte. On a eu l'étoile, papa. Tu l'as vue, toi ? Oui, avec la feuille. On est bien, ici. Sarah tapote l'étoile du doigt. Elle a une trace de nervure. Tu la vois, la trace ? Oui, maman. L'étoile est restée, Sarah. Oui, avec Victorina. L'étoile est restée. Ça sent le platane, un peu tiède. Et la pâte, maman. Oui, dans l'air. La feuille reste sur l'étoile. Un &lt;emphasis level="moderate"&gt;éclat de platane&lt;/emphasis&gt; tient sur la manche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent près de la table. Maman essuie un peu de pâte. On a eu l'étoile, papa. Tu l'as vue, toi ? Oui, avec la feuille. On est bien, ici. Sarah tapote l'étoile du doigt. Elle a une trace de nervure. Tu la vois, la trace ? Oui, maman. L'étoile est restée, Sarah. Oui, avec Victorina. L'étoile est restée. Ça sent le platane, un peu tiède. Et la pâte, maman. Oui, dans l'air. La feuille reste sur l'étoile. Un &lt;emphasis&gt;éclat de platane&lt;/emphasis&gt; tient sur la manche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2010,18 +2101,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2030,12 +2121,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2044,17 +2135,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de platane</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2063,11 +2158,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2076,29 +2171,50 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_la_manche; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'étoile repose sur l'assiette.
-narrateur|La feuille jaune est bien pressée.
-enfant-f|On l'a faite.
-maman|Oui.
-maman|Vous avez pressé l'étoile.
-narrateur|Le givre fond sur le toboggan.</t>
+          <t>narrateur|Ils restent près de la table.
+narrateur|Maman essuie un peu de pâte.
+enfant-f|On a eu l'étoile, papa.
+papa|Tu l'as vue, toi ?
+enfant-f|Oui, avec la feuille.
+maman|On est bien, ici.
+narrateur|Sarah tapote l'étoile du doigt.
+enfant-f|Elle a une trace de nervure.
+maman|Tu la vois, la trace ?
+enfant-f|Oui, maman.
+papa|L'étoile est restée, Sarah.
+enfant-f|Oui, avec Victorina.
+copine|L'étoile est restée.
+narrateur|Ça sent le platane, un peu tiède.
+enfant-f|Et la pâte, maman.
+maman|Oui, dans l'air.
+narrateur|La feuille reste sur l'étoile.
+narrateur|Un éclat de platane tient sur la manche.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>pate</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2204,6 +2320,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
